--- a/data_input/sugc_terrain_constraints_rain.xlsx
+++ b/data_input/sugc_terrain_constraints_rain.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyaez_github_test_env\input\maize_sugarcane_reduction_tables\M5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dario_outputs\maize_sugarcane_reduction_tables\M5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D8FEEF-1857-4FE0-872C-B43DB493109A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63B7C5D-4962-420C-A106-14039369B3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{EE6CACD0-8D83-4948-BDC7-999A08C64FDC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{EE6CACD0-8D83-4948-BDC7-999A08C64FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
